--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487168_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487168_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7804</v>
+        <v>5.0808</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0916</v>
+        <v>4.392</v>
       </c>
       <c r="F2" t="n">
         <v>0.6888</v>
@@ -610,10 +610,10 @@
         <v>0.965</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7416</v>
+        <v>-0.4412</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7588</v>
+        <v>-0.4584</v>
       </c>
       <c r="U2" t="n">
         <v>0.0172</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>H. OREJA ELSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7305</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5476</v>
+        <v>-0.3378</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2781</v>
+        <v>1.2153</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4215</v>
+        <v>1.8253</v>
       </c>
       <c r="H3" t="n">
-        <v>0.119</v>
+        <v>0.4658</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5405</v>
+        <v>1.3595</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3883</v>
+        <v>1.3642</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2793</v>
+        <v>0.7866</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6676</v>
+        <v>0.5777</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0333</v>
+        <v>0.4611</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1604</v>
+        <v>-0.3207</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1271</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.386</v>
+        <v>0.386</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9241</v>
+        <v>-0.7198</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1917</v>
+        <v>-0.737</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.0172</v>
       </c>
       <c r="V3" t="n">
-        <v>0.614</v>
+        <v>-0.614</v>
       </c>
       <c r="W3" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. OREJA ELSO</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6773</v>
+        <v>-0.0449</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5381</v>
+        <v>-0.9482</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2153</v>
+        <v>0.9033</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8253</v>
+        <v>-0.4215</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4658</v>
+        <v>0.119</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3595</v>
+        <v>-0.5405</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3642</v>
+        <v>-0.3883</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7866</v>
+        <v>0.2793</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5777</v>
+        <v>-0.6676</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4611</v>
+        <v>-0.0333</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3207</v>
+        <v>-0.1604</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.1271</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9201</v>
+        <v>0.1487</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9373</v>
+        <v>-0.2089</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0172</v>
+        <v>0.3576</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.614</v>
+        <v>0.614</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1969</v>
+        <v>-0.1233</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3778</v>
+        <v>-0.0228</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1809</v>
+        <v>-0.1005</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3457</v>
@@ -844,13 +844,13 @@
         <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3497</v>
+        <v>0.0294</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4297</v>
+        <v>0.0291</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARBIZU MAIZA</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2592</v>
+        <v>-0.7511</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9799</v>
+        <v>-1.1232</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7207</v>
+        <v>0.3721</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1132</v>
+        <v>-2.6426</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9967</v>
+        <v>-2.8089</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1099</v>
+        <v>0.1664</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2198</v>
+        <v>-0.4478</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0504</v>
+        <v>-1.7337</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2702</v>
+        <v>1.286</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8934</v>
+        <v>-2.1948</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0537</v>
+        <v>-1.0752</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8397</v>
+        <v>-1.1196</v>
       </c>
       <c r="P6" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1231</v>
+        <v>3.2811</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.304</v>
+        <v>-0.9505</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2049</v>
+        <v>-0.5221</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.509</v>
+        <v>-0.4283</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.7418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>A. ARBIZU MAIZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.497</v>
+        <v>-0.8461</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3676</v>
+        <v>-1.781</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1294</v>
+        <v>0.9349</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.786</v>
+        <v>-1.1132</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1477</v>
+        <v>0.9967</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6383</v>
+        <v>-2.1099</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.018</v>
+        <v>-0.2198</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9524</v>
+        <v>1.0504</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-1.2702</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.768</v>
+        <v>-0.8934</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1953</v>
+        <v>-0.0537</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5727</v>
+        <v>-0.8397</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5441</v>
+        <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7449</v>
+        <v>-0.891</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6504</v>
+        <v>-0.5962</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0945</v>
+        <v>-0.2948</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4253</v>
+        <v>-1.0506</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5833</v>
+        <v>-0.7325</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1579</v>
+        <v>-0.3182</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6426</v>
+        <v>-0.8492</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8089</v>
+        <v>0.7038</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1664</v>
+        <v>-1.553</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4478</v>
+        <v>1.0593</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7337</v>
+        <v>2.3131</v>
       </c>
       <c r="L8" t="n">
-        <v>1.286</v>
+        <v>-1.2538</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1948</v>
+        <v>-1.9085</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0752</v>
+        <v>-1.6093</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1196</v>
+        <v>-0.2992</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2811</v>
+        <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6247</v>
+        <v>-0.4643</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9822</v>
+        <v>-0.1246</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6425</v>
+        <v>-0.3398</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4559</v>
+        <v>1.228</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7418</v>
+        <v>1.228</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6108</v>
+        <v>-1.1792</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2926</v>
+        <v>-0.8088</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3182</v>
+        <v>-0.3704</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8492</v>
+        <v>-2.786</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7038</v>
+        <v>-2.1477</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.553</v>
+        <v>-0.6383</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0593</v>
+        <v>-1.018</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3131</v>
+        <v>-0.9524</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2538</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9085</v>
+        <v>-1.768</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6093</v>
+        <v>-1.1953</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2992</v>
+        <v>-0.5727</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0245</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6848</v>
+        <v>0.2092</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3398</v>
+        <v>-0.1464</v>
       </c>
       <c r="V9" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8547</v>
+        <v>-2.6673</v>
       </c>
       <c r="E10" t="n">
         <v>-3.2694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4147</v>
+        <v>0.6021</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3524</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.197</v>
+        <v>-1.0097</v>
       </c>
       <c r="T10" t="n">
         <v>-0.7139</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4832</v>
+        <v>-0.2958</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6562</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.095</v>
+        <v>-3.9274</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0518</v>
+        <v>-2.7934</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0433</v>
+        <v>-1.1339</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-5.7566</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1852</v>
+        <v>-1.3868</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0889</v>
+        <v>-4.3698</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3179</v>
+        <v>-2.7805</v>
       </c>
       <c r="K11" t="n">
-        <v>0.626</v>
+        <v>-0.1915</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6919</v>
+        <v>-2.589</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2216</v>
+        <v>-2.9761</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4408</v>
+        <v>-1.1953</v>
       </c>
       <c r="O11" t="n">
         <v>-1.7808</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.193</v>
+        <v>2.3161</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7021</v>
+        <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8282</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8183</v>
+        <v>-0.2987</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.4739</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1701</v>
+        <v>0.2859</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.548</v>
+        <v>-3.976</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2535</v>
+        <v>-2.6919</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2946</v>
+        <v>-1.2842</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.7566</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3868</v>
+        <v>0.1852</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.3698</v>
+        <v>-1.0889</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.7805</v>
+        <v>1.3179</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1915</v>
+        <v>0.626</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.589</v>
+        <v>0.6919</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9761</v>
+        <v>-2.2216</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1953</v>
+        <v>-0.4408</v>
       </c>
       <c r="O12" t="n">
         <v>-1.7808</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3161</v>
+        <v>-0.193</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3161</v>
+        <v>2.7021</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3934</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7588</v>
+        <v>-0.4584</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.2509</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2859</v>
+        <v>-2.1701</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2859</v>
+        <v>-0.6562</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.9049</v>
+        <v>-8.607600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.4144</v>
+        <v>-10.117</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5091</v>
+        <v>1.5093</v>
       </c>
       <c r="G13" t="n">
         <v>-13.2445</v>
@@ -1441,19 +1441,19 @@
         <v>-9.539200000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6697000000000002</v>
+        <v>-0.6696999999999997</v>
       </c>
       <c r="K13" t="n">
         <v>3.8749</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.5445</v>
+        <v>-4.544499999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-12.575</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.5801</v>
+        <v>-7.580100000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-4.9948</v>
@@ -1468,13 +1468,13 @@
         <v>18.3358</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.0148</v>
+        <v>-5.7175</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.1774</v>
+        <v>-3.8799</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8377</v>
+        <v>-1.8376</v>
       </c>
       <c r="V13" t="n">
         <v>3.599400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.11</v>
+        <v>7.3761</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0986</v>
+        <v>3.4991</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0114</v>
+        <v>3.8769</v>
       </c>
       <c r="G14" t="n">
         <v>6.0981</v>
@@ -1546,13 +1546,13 @@
         <v>1.7371</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4329</v>
+        <v>0.699</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6398</v>
+        <v>-0.2393</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0727</v>
+        <v>0.9382</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4067</v>
+        <v>5.8031</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5072</v>
+        <v>3.2082</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8996</v>
+        <v>2.5949</v>
       </c>
       <c r="G15" t="n">
         <v>5.2354</v>
@@ -1624,13 +1624,13 @@
         <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9915</v>
+        <v>0.4049</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6993</v>
+        <v>0.0017</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2922</v>
+        <v>0.4032</v>
       </c>
       <c r="V15" t="n">
         <v>1.5138</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1887</v>
+        <v>2.9899</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7071</v>
+        <v>1.8647</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4817</v>
+        <v>1.1252</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5697</v>
+        <v>2.0116</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1737</v>
+        <v>1.7367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6041</v>
+        <v>0.2749</v>
       </c>
       <c r="J16" t="n">
-        <v>0.498</v>
+        <v>1.3376</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2588</v>
+        <v>2.665</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7569</v>
+        <v>-1.3273</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0677</v>
+        <v>0.674</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9149</v>
+        <v>-0.9283</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1528</v>
+        <v>1.6022</v>
       </c>
       <c r="P16" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R16" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1794</v>
+        <v>0.6273</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2091</v>
+        <v>0.1061</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.5212</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.861</v>
+        <v>1.5121</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1637</v>
+        <v>1.4052</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6972</v>
+        <v>0.1069</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0116</v>
+        <v>-0.5697</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7367</v>
+        <v>-1.1737</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2749</v>
+        <v>0.6041</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3376</v>
+        <v>0.498</v>
       </c>
       <c r="K17" t="n">
-        <v>2.665</v>
+        <v>-0.2588</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3273</v>
+        <v>0.7569</v>
       </c>
       <c r="M17" t="n">
-        <v>0.674</v>
+        <v>-1.0677</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9283</v>
+        <v>-0.9149</v>
       </c>
       <c r="O17" t="n">
-        <v>1.6022</v>
+        <v>-0.1528</v>
       </c>
       <c r="P17" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5017</v>
+        <v>1.5028</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5949</v>
+        <v>0.9072</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.5955</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9902</v>
+        <v>0.897</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2966</v>
+        <v>1.0963</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3064</v>
+        <v>-0.1993</v>
       </c>
       <c r="G18" t="n">
         <v>0.6822</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0801</v>
+        <v>0.9869</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.778</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1018</v>
+        <v>0.2089</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1074</v>
+        <v>0.0281</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3061</v>
+        <v>-2.7052</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1987</v>
+        <v>2.7334</v>
       </c>
       <c r="G19" t="n">
         <v>0.7271</v>
@@ -1936,13 +1936,13 @@
         <v>1.7371</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5486</v>
+        <v>0.587</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5803</v>
+        <v>0.0205</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0317</v>
+        <v>0.5664</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8999</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4395</v>
+        <v>-1.6575</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3073</v>
+        <v>-1.7525</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8679</v>
+        <v>0.095</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9916</v>
+        <v>-0.3744</v>
       </c>
       <c r="H20" t="n">
-        <v>0.179</v>
+        <v>0.2361</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8125</v>
+        <v>-0.6105</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6104000000000001</v>
+        <v>-0.3813</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2279</v>
+        <v>0.0828</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8383</v>
+        <v>-0.4641</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3812</v>
+        <v>0.0069</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4069</v>
+        <v>0.1533</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0257</v>
+        <v>-0.1464</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.8602</v>
+        <v>0.193</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.7902</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0431</v>
+        <v>0.3235</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2586</v>
+        <v>-0.4062</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7845</v>
+        <v>0.7297</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.614</v>
+        <v>-1.7997</v>
       </c>
       <c r="W20" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4629</v>
+        <v>-2.0981</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8526</v>
+        <v>-2.628</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3898</v>
+        <v>0.5299</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3744</v>
+        <v>-1.3403</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2361</v>
+        <v>-0.8041</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6105</v>
+        <v>-0.5362</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3813</v>
+        <v>-0.6662</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0828</v>
+        <v>0.1242</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4641</v>
+        <v>-0.7904</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0069</v>
+        <v>-0.6741</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1533</v>
+        <v>-0.9283</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1464</v>
+        <v>0.2542</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5182</v>
+        <v>0.4002</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5063</v>
+        <v>-0.0317</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0245</v>
+        <v>0.4319</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3029</v>
+        <v>-2.2611</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1885</v>
+        <v>-4.2086</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1144</v>
+        <v>1.9475</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2169</v>
+        <v>0.9916</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.304</v>
+        <v>0.179</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0871</v>
+        <v>0.8125</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2974</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9885</v>
+        <v>-0.2279</v>
       </c>
       <c r="L22" t="n">
-        <v>1.286</v>
+        <v>0.8383</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5143</v>
+        <v>0.3812</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3154</v>
+        <v>0.4069</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8011</v>
+        <v>-0.0257</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5441</v>
+        <v>-3.8602</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9301</v>
+        <v>-5.7902</v>
       </c>
       <c r="R22" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6438</v>
+        <v>1.2215</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4442</v>
+        <v>0.3573</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1996</v>
+        <v>0.8642</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1857</v>
+        <v>-0.614</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1857</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.339</v>
+        <v>-2.3495</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.628</v>
+        <v>-1.2886</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2889</v>
+        <v>-1.0609</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3403</v>
+        <v>-0.2169</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8041</v>
+        <v>-2.304</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5362</v>
+        <v>2.0871</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6662</v>
+        <v>0.2974</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1242</v>
+        <v>-0.9885</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7904</v>
+        <v>1.286</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6741</v>
+        <v>-0.5143</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9283</v>
+        <v>-1.3154</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2542</v>
+        <v>0.8011</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.158</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1593</v>
+        <v>0.5972</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0317</v>
+        <v>0.3441</v>
       </c>
       <c r="U23" t="n">
-        <v>0.191</v>
+        <v>0.2531</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.9049</v>
+        <v>10.2401</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.509299999999999</v>
+        <v>-1.5094</v>
       </c>
       <c r="F24" t="n">
-        <v>10.4144</v>
+        <v>11.7495</v>
       </c>
       <c r="G24" t="n">
         <v>13.2447</v>
       </c>
       <c r="H24" t="n">
-        <v>3.705299999999999</v>
+        <v>3.7053</v>
       </c>
       <c r="I24" t="n">
-        <v>9.539300000000001</v>
+        <v>9.539299999999999</v>
       </c>
       <c r="J24" t="n">
         <v>12.5751</v>
@@ -2308,7 +2308,7 @@
         <v>4.9948</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6696999999999999</v>
+        <v>0.6697</v>
       </c>
       <c r="N24" t="n">
         <v>-3.8749</v>
@@ -2326,13 +2326,13 @@
         <v>11.5804</v>
       </c>
       <c r="S24" t="n">
-        <v>6.015</v>
+        <v>7.350299999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>1.837899999999999</v>
+        <v>1.8377</v>
       </c>
       <c r="U24" t="n">
-        <v>4.1771</v>
+        <v>5.5123</v>
       </c>
       <c r="V24" t="n">
         <v>-3.5995</v>
